--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -728,10 +728,10 @@
         <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
         <v>2.74</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="O2" t="n">
         <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
         <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="P2" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.57</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
         <v>2.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -728,55 +728,55 @@
         <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
         <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
         <v>1.6</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -758,31 +758,31 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.74</v>
+        <v>3.88</v>
       </c>
       <c r="AA2" t="n">
         <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.44</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-06-11.xlsx
+++ b/jogos_2026-06-11.xlsx
@@ -705,23 +705,23 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '63', '90+1']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46184.58333333334</v>
